--- a/processed_ruby_restored_xlsx/sc228_瑠璃Ａ：ボテ腹Ｈ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc228_瑠璃Ａ：ボテ腹Ｈ.ss.xlsx
@@ -713,8 +713,8 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>「Haha... it's too early to be decided already—we don't
-even know if it's a boy or a girl...！」</t>
+          <t>「Haha... it's too early to be decided already—we
+don't even know if it's a boy or a girl...！」</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -896,8 +896,8 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>「...Being patted and fussed over by Oji-sama, the baby
-in my belly is enjoying it too, you know.」</t>
+          <t>「...Being patted and fussed over by Oji-sama, the
+baby in my belly is enjoying it too, you know.」</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -957,8 +957,9 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>「Yes, even just now... ah！ I gave my tummy a wee kick！
-You too, Oji-sama... here, put your ear to it...」</t>
+          <t>「Yes, even just now... ah！ I gave my tummy a wee
+kick！ You too, Oji-sama... here, put your ear to
+it...」</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1558,8 +1559,8 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Hearing my words, Rurichiyo-chan let out an absolutely
-delighted smile.</t>
+          <t>Hearing my words, Rurichiyo-chan let out an
+absolutely delighted smile.</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1865,7 +1866,8 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>But Rurichiyo-chan's cheeks are still adorably puffed.</t>
+          <t>But Rurichiyo-chan's cheeks are still adorably
+puffed.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2369,7 +2371,8 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>That made me so embarrassed my face kept getting hot….</t>
+          <t>That made me so embarrassed my face kept getting
+hot….</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2568,7 +2571,8 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>...I closed my eyes and kissed her softly and quietly.</t>
+          <t>...I closed my eyes and kissed her softly and
+quietly.</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2643,8 +2647,8 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>Having Rurichiyo-chan by my side like this... that was
-my greatest happiness.</t>
+          <t>Having Rurichiyo-chan by my side like this... that
+was my greatest happiness.</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -3345,8 +3349,8 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan adopts a soft, gentle expression like a
-mother soothing a child.</t>
+          <t>Rurichiyo-chan adopts a soft, gentle expression like
+a mother soothing a child.</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3437,8 +3441,8 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>Saying that, I gave a tiny kiss to the most protruding
-part of her belly….</t>
+          <t>Saying that, I gave a tiny kiss to the most
+protruding part of her belly….</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3710,7 +3714,8 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>Because Mama sulked, I gave my clingy Mama a kiss too.</t>
+          <t>Because Mama sulked, I gave my clingy Mama a kiss
+too.</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3725,8 +3730,8 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>Mom's face has gone all soft and melting, and her eyes
-are all droopy and half-closed.</t>
+          <t>Mom's face has gone all soft and melting, and her
+eyes are all droopy and half-closed.</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -4290,7 +4295,8 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>This time she plants a kiss on my warm, flushed cheek.</t>
+          <t>This time she plants a kiss on my warm, flushed
+cheek.</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4487,8 +4493,8 @@
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>Before I know it my mouth is hanging open, and a slack
-sound escapes from me.</t>
+          <t>Before I know it my mouth is hanging open, and a
+slack sound escapes from me.</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4882,8 +4888,8 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>I, anxious while trying to brush it off, take her hand
-to try to remove our mutual unease.</t>
+          <t>I, anxious while trying to brush it off, take her
+hand to try to remove our mutual unease.</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -5753,8 +5759,8 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>I nodded obediently to Mama's words and slowly matched
-her movement.</t>
+          <t>I nodded obediently to Mama's words and slowly
+matched her movement.</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -6059,8 +6065,8 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan moves at her own pace and breathes out,
-but she’s properly watching me too.</t>
+          <t>Rurichiyo-chan moves at her own pace and breathes
+out, but she’s properly watching me too.</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -6229,7 +6235,8 @@
       <c r="B378" s="1" t="inlineStr">
         <is>
           <t>With a wet, squelching “jubutto,” it’s overflowing
-enough to spill out from the gap where they’re joined.</t>
+enough to spill out from the gap where they’re
+joined.</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -7041,8 +7048,8 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t>I feel a sure maternal love from Mama, and my body and
-heart are being wrapped up warmly.</t>
+          <t>I feel a sure maternal love from Mama, and my body
+and heart are being wrapped up warmly.</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -7412,8 +7419,8 @@
       </c>
       <c r="B455" s="1" t="inlineStr">
         <is>
-          <t>Just as my hips had lifted to the brink of coming, she
-slowly, slowly sank her body down.</t>
+          <t>Just as my hips had lifted to the brink of coming,
+she slowly, slowly sank her body down.</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7520,8 +7527,8 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t>Even though the movements are gentle, my body trembles
-with pleasure.</t>
+          <t>Even though the movements are gentle, my body
+trembles with pleasure.</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7581,8 +7588,8 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>「Yeah, Mama... that feeling just now... it felt really
-good...」</t>
+          <t>「Yeah, Mama... that feeling just now... it felt
+really good...」</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -7704,8 +7711,8 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>This time they shift the angle of their hips to adjust
-so I can feel it even more.</t>
+          <t>This time they shift the angle of their hips to
+adjust so I can feel it even more.</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -8271,8 +8278,8 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>When I take in Mama's feelings, I want to be even more
-clingy.</t>
+          <t>When I take in Mama's feelings, I want to be even
+more clingy.</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -8455,8 +8462,8 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>She just got startled by the suddenness, but she seems
-fine.</t>
+          <t>She just got startled by the suddenness, but she
+seems fine.</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8577,8 +8584,8 @@
       </c>
       <c r="B531" s="1" t="inlineStr">
         <is>
-          <t>Being called "cute" feels a bit strange, but when Mama
-says it, it doesn't feel bad.</t>
+          <t>Being called "cute" feels a bit strange, but when
+Mama says it, it doesn't feel bad.</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -8930,9 +8937,9 @@
       </c>
       <c r="B554" s="1" t="inlineStr">
         <is>
-          <t>I stopped moving because I worried she was feeling too
-much, but even so Mom looks like she feels incredibly
-good.</t>
+          <t>I stopped moving because I worried she was feeling
+too much, but even so Mom looks like she feels
+incredibly good.</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -9234,8 +9241,8 @@
       </c>
       <c r="B574" s="1" t="inlineStr">
         <is>
-          <t>Even though I’m overwhelmed by how much she’s feeling,
-I use my whole body to support Mom.</t>
+          <t>Even though I’m overwhelmed by how much she’s
+feeling, I use my whole body to support Mom.</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -9508,8 +9515,8 @@
       </c>
       <c r="B592" s="1" t="inlineStr">
         <is>
-          <t>The more we say it, the more my head melts, but I want
-to say 'I love you' a lot, and hear it too.</t>
+          <t>The more we say it, the more my head melts, but I
+want to say 'I love you' a lot, and hear it too.</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -9768,8 +9775,8 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>Being soothed by gentle words, my self-control finally
-broke.</t>
+          <t>Being soothed by gentle words, my self-control
+finally broke.</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -9953,8 +9960,8 @@
       <c r="B621" s="1" t="inlineStr">
         <is>
           <t>Just before reaching orgasm, an electrical signal
-trying to resist the pleasure runs through me, and the
-brain's limiter kicks in.</t>
+trying to resist the pleasure runs through me, and
+the brain's limiter kicks in.</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -10169,8 +10176,8 @@
       </c>
       <c r="B635" s="1" t="inlineStr">
         <is>
-          <t>「Haa, huu... Mama, nn！ Ha！ You're pouring so much into
-me...」</t>
+          <t>「Haa, huu... Mama, nn！ Ha！ You're pouring so much
+into me...」</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -10201,7 +10208,8 @@
       <c r="B637" s="1" t="inlineStr">
         <is>
           <t>「Huu... I'm feeling it... ahhn！ Oji-sama's... thick
-stuff, all the way to the entrance of my pussy... ah！」</t>
+stuff, all the way to the entrance of my pussy...
+ah！」</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -10555,8 +10563,8 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>「Hafa... haa, you came a lot... pyu-pyu, didn't you...
-Good job...」</t>
+          <t>「Hafa... haa, you came a lot... pyu-pyu, didn't
+you... Good job...」</t>
         </is>
       </c>
       <c r="C660" t="n">

--- a/processed_ruby_restored_xlsx/sc228_瑠璃Ａ：ボテ腹Ｈ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc228_瑠璃Ａ：ボテ腹Ｈ.ss.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>「What?! You're already moving?!」</t>
+          <t>What?! You're already moving?!</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1268,8 +1268,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>「Well... it's little by little, but I'm starting to
-really feel it.」</t>
+          <t>Well... it's little by little, but I'm starting to
+really feel it.</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2172,9 +2172,9 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>「Oh, come on... you shouldn't be all shy, you know？
+          <t>Oh, come on... you shouldn't be all shy, you know？
 It's totally uncool to be embarrassed in front of the
-baby...！」</t>
+baby...！</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>「Mama... Ma-maaa！」</t>
+          <t>Mama... Ma-maaa！</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -3058,8 +3058,8 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>「Smooch！ Schmu—ch！ Smooch！ Smooch！ Nnnh… smooch！
-Smooch！」</t>
+          <t>Smooch！ Schmu—ch！ Smooch！ Smooch！ Nnnh… smooch！
+Smooch！</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>Saying that, I gave a tiny kiss to the most
+          <t>Saying that, he gave a tiny kiss to the most
 protruding part of her belly….</t>
         </is>
       </c>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>When I kissed it again, her belly gave a little
+          <t>When he kissed it again, her belly gave a little
 twitch.</t>
         </is>
       </c>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>「smooch！ mm… smooch smooch… smooch」</t>
+          <t>smooch！ mm… smooch smooch… smooch</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3974,8 +3974,8 @@
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>「Faah… my body's getting hot… nngh！ chu—... chupu,
-chuppaa…」</t>
+          <t>Faah… my body's getting hot… nngh！ chu—... chupu,
+chuppaa…</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>「Fwaaahh...」</t>
+          <t>Fwaaahh...</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama... smooch, smooch！ Smooooch...」</t>
+          <t>Oji-sama... smooch, smooch！ Smooooch...</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>「Ahh... nn！ I'm getting even hotter...」</t>
+          <t>Ahh... nn！ I'm getting even hotter...</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>Then Mama rushed at me as if she couldn't stand it
+          <t>Then Mama rushed at him as if she couldn't stand it
 anymore.</t>
         </is>
       </c>
@@ -6004,8 +6004,8 @@
       </c>
       <c r="B363" s="1" t="inlineStr">
         <is>
-          <t>Then, once the right rhythm is found, my penis begins
-to throb inside Mama.</t>
+          <t>Then, once the right rhythm is found, his penis
+begins to throb inside Mama.</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>My penis is definitely getting more sensitive.</t>
+          <t>His penis is definitely getting more sensitive.</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>「Fwaa... Mama...？！」</t>
+          <t>Fwaa... Mama...？！</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t>「Nngh... okay—did I do it right...？」</t>
+          <t>Nngh... okay—did I do it right...？</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t>Even so, she keeps staring at me intently.</t>
+          <t>Even so, they keep staring at me intently.</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -7250,8 +7250,8 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t>「Mmm—hah, huff… more, more… shall we get even
-naughtier？」</t>
+          <t>Mmm—hah, huff… more, more… shall we get even
+naughtier？</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t>「Mmm, ah... ah, yeah...」</t>
+          <t>Mmm, ah... ah, yeah...</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>As Mama slowly lifts her hips, my penis also rises,
+          <t>As Mama slowly lifts her hips, her penis also rises,
 pushed up while feeling a comfortable, just-right
 squeeze.</t>
         </is>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="B454" s="1" t="inlineStr">
         <is>
-          <t>「Huu, fufu...！ I won't tell, okay...？」</t>
+          <t>Huu, fufu...！ I won't tell, okay...？</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -7420,7 +7420,7 @@
       <c r="B455" s="1" t="inlineStr">
         <is>
           <t>Just as my hips had lifted to the brink of coming,
-she slowly, slowly sank her body down.</t>
+they slowly, slowly sank their body down.</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>「Hah, heheh... nnh-hehe...！」</t>
+          <t>Hah, heheh... nnh-hehe...！</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>Her small body sank down, and with my penis still
+          <t>Her small body sank down, and with his penis still
 wrapped inside her she began grinding her hips.</t>
         </is>
       </c>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>「Hah, haaah… my head's starting to melt…」</t>
+          <t>Hah, haaah… my head」s starting to melt…</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B515" s="1" t="inlineStr">
         <is>
-          <t>「Fugu！　Fuaaaaah！」</t>
+          <t>Fugu！　Fuaaaaah！</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -8355,8 +8355,8 @@
       </c>
       <c r="B516" s="1" t="inlineStr">
         <is>
-          <t>The moment I thrust my hips up, Mama let out a voice
-that made her throat quiver.</t>
+          <t>The moment he thrust his hips up, Mama let out a
+voice that made her throat quiver.</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>But her expression has gone all dazed and slack.</t>
+          <t>But their expression has gone all dazed and slack.</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8462,8 +8462,8 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>She just got startled by the suddenness, but she
-seems fine.</t>
+          <t>They just got startled by the suddenness, but they
+seem fine.</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8892,7 +8892,7 @@
       <c r="B551" s="1" t="inlineStr">
         <is>
           <t>I might be seeing this expression for the first
-time...！？</t>
+time...！？"</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nn！ Oji-sama…」</t>
+          <t>Nn, nn！ Oji-sama…</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="B587" s="1" t="inlineStr">
         <is>
-          <t>「Wah! I like you more... muuch more!」</t>
+          <t>Wah! I like you more... muuch more!</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -9638,7 +9638,7 @@
       <c r="B600" s="1" t="inlineStr">
         <is>
           <t>「About Oji-sama... always... ahhh, hafu！ I think of
-me... you know...」</t>
+him... you know...」</t>
         </is>
       </c>
       <c r="C600" t="n">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="B608" s="1" t="inlineStr">
         <is>
-          <t>「Haa, haaah... Mama！ Mama！ Mama！ Mamaah！」</t>
+          <t>Haa, haaah... Mama！ Mama！ Mama！ Mamaah！</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -9837,8 +9837,8 @@
       </c>
       <c r="B613" s="1" t="inlineStr">
         <is>
-          <t>「Hah, hah, fuu... fufu！  So then, lots... lots of
-pyu-pyu, okay~？  Fuu, uun！」</t>
+          <t>Hah, hah, fuu... fufu！  So then, lots... lots of
+pyu-pyu, okay~？  Fuu, uun！</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -10176,8 +10176,8 @@
       </c>
       <c r="B635" s="1" t="inlineStr">
         <is>
-          <t>「Haa, huu... Mama, nn！ Ha！ You're pouring so much
-into me...」</t>
+          <t>Haa, huu... Mama, nn！ Ha！ You're pouring so much into
+me...</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -10240,8 +10240,9 @@
       </c>
       <c r="B639" s="1" t="inlineStr">
         <is>
-          <t>I’ve made her face go shamelessly dazed, and I really
-think she’s just soaking herself in pleasure.</t>
+          <t>I’ve made their face go shamelessly dazed, and I
+really think they’re just soaking themselves in
+pleasure.</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -10302,8 +10303,8 @@
       </c>
       <c r="B643" s="1" t="inlineStr">
         <is>
-          <t>「Hahhh…！ Now, all of it… pyu, pyu…！ Pyu-pyu, let's do
-it…？」</t>
+          <t>Hahhh…！ Now, all of it… pyu, pyu…！ Pyu-pyu, let」s do
+it…？</t>
         </is>
       </c>
       <c r="C643" t="n">
@@ -10563,8 +10564,8 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>「Hafa... haa, you came a lot... pyu-pyu, didn't
-you... Good job...」</t>
+          <t>Hafa... haa, you came a lot... pyu-pyu, didn't you...
+Good job...</t>
         </is>
       </c>
       <c r="C660" t="n">
